--- a/admin/members.xlsx
+++ b/admin/members.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stranger/git/statlab/admin/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62E99E1B-D748-7448-84C2-1C30686E6E86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0D003C1-4E93-4749-9DDD-5BD87EB626D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="900" windowWidth="28040" windowHeight="17180" xr2:uid="{5F07C459-020D-B749-8C16-B3733F7EA3BC}"/>
+    <workbookView xWindow="1100" yWindow="900" windowWidth="20100" windowHeight="17180" xr2:uid="{5F07C459-020D-B749-8C16-B3733F7EA3BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="101">
   <si>
     <t>name</t>
   </si>
@@ -333,6 +333,15 @@
   </si>
   <si>
     <t>goikon@math.uoa.gr</t>
+  </si>
+  <si>
+    <t>Νικόλας</t>
+  </si>
+  <si>
+    <t>Καλατζής</t>
+  </si>
+  <si>
+    <t>nkalat98@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -715,19 +724,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0789593-D708-6A44-90EF-49129EE32215}">
-  <dimension ref="A2:D32"/>
+  <dimension ref="A2:D33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.83203125" customWidth="1"/>
-    <col min="2" max="2" width="19.33203125" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" customWidth="1"/>
+    <col min="2" max="2" width="19.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1</v>
       </c>
       <c r="C2" t="s">
         <v>2</v>
@@ -738,439 +747,456 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>90</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>56</v>
+        <v>34</v>
+      </c>
+      <c r="D3" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>58</v>
+        <v>42</v>
+      </c>
+      <c r="D5" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>59</v>
+        <v>34</v>
+      </c>
+      <c r="D6" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="C7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>60</v>
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>74</v>
+        <v>42</v>
+      </c>
+      <c r="D8" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>82</v>
+        <v>42</v>
+      </c>
+      <c r="D10" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>93</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="C11" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>76</v>
+        <v>34</v>
+      </c>
+      <c r="D11" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>77</v>
+        <v>42</v>
+      </c>
+      <c r="D12" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>78</v>
+        <v>34</v>
+      </c>
+      <c r="D13" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>62</v>
+        <v>72</v>
+      </c>
+      <c r="D15" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D16" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
-      </c>
-      <c r="D17" t="s">
-        <v>66</v>
+        <v>6</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>42</v>
-      </c>
-      <c r="D18" t="s">
-        <v>64</v>
+        <v>6</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" t="s">
         <v>26</v>
       </c>
-      <c r="B19" t="s">
-        <v>41</v>
-      </c>
       <c r="C19" t="s">
-        <v>42</v>
-      </c>
-      <c r="D19" t="s">
-        <v>54</v>
+        <v>34</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
-      </c>
-      <c r="D20" t="s">
-        <v>61</v>
+        <v>6</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>39</v>
+        <v>96</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="C21" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="D21" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>42</v>
-      </c>
-      <c r="D22" t="s">
-        <v>65</v>
+        <v>6</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="B23" t="s">
-        <v>46</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="D23" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>42</v>
-      </c>
-      <c r="D24" t="s">
-        <v>52</v>
+        <v>6</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="C25" t="s">
-        <v>42</v>
-      </c>
-      <c r="D25" t="s">
-        <v>51</v>
+        <v>6</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="B26" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="C26" t="s">
         <v>42</v>
       </c>
       <c r="D26" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="C27" t="s">
-        <v>72</v>
-      </c>
-      <c r="D27" t="s">
-        <v>73</v>
+        <v>34</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="B28" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="D28" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>87</v>
+        <v>15</v>
       </c>
       <c r="C29" t="s">
-        <v>72</v>
-      </c>
-      <c r="D29" t="s">
-        <v>88</v>
+        <v>6</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C30" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D30" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>92</v>
+        <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>30</v>
       </c>
       <c r="C31" t="s">
         <v>34</v>
       </c>
       <c r="D31" t="s">
-        <v>94</v>
+        <v>63</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B32" t="s">
-        <v>96</v>
+        <v>26</v>
       </c>
       <c r="C32" t="s">
         <v>72</v>
       </c>
       <c r="D32" t="s">
-        <v>97</v>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>20</v>
+      </c>
+      <c r="B33" t="s">
+        <v>19</v>
+      </c>
+      <c r="C33" t="s">
+        <v>6</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D33">
+    <sortCondition ref="A3:A33"/>
+  </sortState>
   <hyperlinks>
-    <hyperlink ref="D3" r:id="rId1" xr:uid="{4A9B617A-114C-6C41-8E5F-7431D92EFBAF}"/>
-    <hyperlink ref="D4" r:id="rId2" xr:uid="{735F08AB-D272-0348-83FE-D6F122727234}"/>
-    <hyperlink ref="D5" r:id="rId3" xr:uid="{7D70BA24-679E-FE46-AC50-2BFFB641ED0E}"/>
-    <hyperlink ref="D6" r:id="rId4" xr:uid="{DA9BCE54-323F-E34A-936B-6B088B8BE447}"/>
-    <hyperlink ref="D7" r:id="rId5" xr:uid="{CB0AE925-6A64-724D-BD05-1165A60FBE1E}"/>
-    <hyperlink ref="D8" r:id="rId6" xr:uid="{10404AE4-036C-2746-876D-9938ACBC79D6}"/>
-    <hyperlink ref="D9" r:id="rId7" xr:uid="{3DDF1D75-097E-A740-8FB2-11E22CFA8DDC}"/>
-    <hyperlink ref="D11" r:id="rId8" xr:uid="{9EFABA5B-B1B1-2B41-9913-64C1863A4DFD}"/>
-    <hyperlink ref="D12" r:id="rId9" xr:uid="{752BD828-1F73-CB44-8016-3BFC894C8573}"/>
-    <hyperlink ref="D13" r:id="rId10" xr:uid="{AD6BAE3B-99FB-DC44-BAA4-CCDC56172165}"/>
-    <hyperlink ref="D14" r:id="rId11" xr:uid="{CF8ADF8E-6533-7D4F-9581-C0DCF7E785E7}"/>
-    <hyperlink ref="D15" r:id="rId12" xr:uid="{60DF5EF2-C291-8A48-8220-8EA45AB792AE}"/>
-    <hyperlink ref="D10" r:id="rId13" xr:uid="{7956838E-02CC-5B4A-9D5C-1D2C708190DF}"/>
+    <hyperlink ref="D22" r:id="rId1" xr:uid="{4A9B617A-114C-6C41-8E5F-7431D92EFBAF}"/>
+    <hyperlink ref="D25" r:id="rId2" xr:uid="{735F08AB-D272-0348-83FE-D6F122727234}"/>
+    <hyperlink ref="D17" r:id="rId3" xr:uid="{7D70BA24-679E-FE46-AC50-2BFFB641ED0E}"/>
+    <hyperlink ref="D18" r:id="rId4" xr:uid="{DA9BCE54-323F-E34A-936B-6B088B8BE447}"/>
+    <hyperlink ref="D24" r:id="rId5" xr:uid="{CB0AE925-6A64-724D-BD05-1165A60FBE1E}"/>
+    <hyperlink ref="D29" r:id="rId6" xr:uid="{10404AE4-036C-2746-876D-9938ACBC79D6}"/>
+    <hyperlink ref="D20" r:id="rId7" xr:uid="{3DDF1D75-097E-A740-8FB2-11E22CFA8DDC}"/>
+    <hyperlink ref="D33" r:id="rId8" xr:uid="{9EFABA5B-B1B1-2B41-9913-64C1863A4DFD}"/>
+    <hyperlink ref="D14" r:id="rId9" xr:uid="{752BD828-1F73-CB44-8016-3BFC894C8573}"/>
+    <hyperlink ref="D9" r:id="rId10" xr:uid="{AD6BAE3B-99FB-DC44-BAA4-CCDC56172165}"/>
+    <hyperlink ref="D19" r:id="rId11" xr:uid="{CF8ADF8E-6533-7D4F-9581-C0DCF7E785E7}"/>
+    <hyperlink ref="D27" r:id="rId12" xr:uid="{60DF5EF2-C291-8A48-8220-8EA45AB792AE}"/>
+    <hyperlink ref="D4" r:id="rId13" xr:uid="{7956838E-02CC-5B4A-9D5C-1D2C708190DF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
